--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512476_ELIMINGRE14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512476_ELIMINGRE14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.0453</v>
+        <v>10.9204</v>
       </c>
       <c r="E2" t="n">
-        <v>14.6724</v>
+        <v>13.2893</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6271</v>
+        <v>-2.3689</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0197</v>
+        <v>3.063</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7367</v>
+        <v>2.8347</v>
       </c>
       <c r="I2" t="n">
-        <v>0.283</v>
+        <v>0.2282</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0858</v>
+        <v>6.3457</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6441</v>
+        <v>4.8623</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4417</v>
+        <v>1.4834</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.0661</v>
+        <v>-3.2827</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.9074</v>
+        <v>-2.0276</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.1587</v>
+        <v>-1.2552</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>3.486</v>
+        <v>1.2842</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9278</v>
+        <v>1.1694</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5581</v>
+        <v>0.1149</v>
       </c>
       <c r="V2" t="n">
-        <v>4.339</v>
+        <v>4.4311</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6588</v>
+        <v>5.7742</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.3197</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6047</v>
+        <v>2.688</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7714</v>
+        <v>2.6757</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8333</v>
+        <v>0.0124</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5244</v>
+        <v>-0.526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0618</v>
+        <v>0.095</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.621</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0271</v>
+        <v>1.162</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3053</v>
+        <v>0.4081</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7218</v>
+        <v>0.7539</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5515</v>
+        <v>-1.688</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2435</v>
+        <v>-0.3131</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.308</v>
+        <v>-1.3749</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1491</v>
+        <v>1.2388</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3453</v>
+        <v>1.0189</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8038</v>
+        <v>0.2199</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7803</v>
+        <v>2.7542</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3995</v>
+        <v>2.4421</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3807</v>
+        <v>0.3121</v>
       </c>
     </row>
     <row r="4">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7997</v>
+        <v>1.8316</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1833</v>
+        <v>1.7964</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4935</v>
+        <v>4.0895</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3101</v>
+        <v>-2.2931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1668</v>
+        <v>0.1619</v>
       </c>
       <c r="H5" t="n">
-        <v>1.7003</v>
+        <v>1.6887</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5335</v>
+        <v>-1.5269</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9249</v>
+        <v>3.0697</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8792</v>
+        <v>2.9558</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0457</v>
+        <v>0.1139</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7581</v>
+        <v>-2.9078</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5792</v>
+        <v>-1.6407</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0841</v>
+        <v>-0.4049</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6312</v>
+        <v>-0.2012</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4529</v>
+        <v>-0.2037</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9003</v>
+        <v>0.871</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1998</v>
+        <v>1.2211</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2995</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MARTINEZ JURADO</t>
+          <t>P. LUENGO MATEO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2716</v>
+        <v>1.1775</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0067</v>
+        <v>0.3572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2649</v>
+        <v>0.8203</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1425</v>
+        <v>-1.2544</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2712</v>
+        <v>0.4972</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1287</v>
+        <v>-1.7515</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0.2861</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.2932</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.5793</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1425</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2712</v>
+        <v>-0.796</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1287</v>
+        <v>-0.1723</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>1.9474</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0709</v>
+        <v>0.6066</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0067</v>
+        <v>0.6433</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0776</v>
+        <v>-0.0367</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. FAYE</t>
+          <t>D. MARTINEZ JURADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2332</v>
+        <v>0.3365</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2828</v>
+        <v>0.0092</v>
       </c>
       <c r="F7" t="n">
-        <v>0.516</v>
+        <v>0.3273</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9016999999999999</v>
+        <v>0.1263</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9223</v>
+        <v>0.2658</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0206</v>
+        <v>-0.1395</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3363</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3363</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5654</v>
+        <v>0.1263</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.586</v>
+        <v>0.2658</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0206</v>
+        <v>-0.1395</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3947</v>
+        <v>0.0155</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0538</v>
+        <v>0.0092</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3409</v>
+        <v>0.0062</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>P. FAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4435</v>
+        <v>0.1632</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7703</v>
+        <v>-0.2462</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3268</v>
+        <v>0.4093</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.9413</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4999</v>
+        <v>-0.9216</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3081</v>
+        <v>-0.0197</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6217</v>
+        <v>-0.2822</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4217</v>
+        <v>-0.2822</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4297</v>
+        <v>-0.6591</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9215</v>
+        <v>-0.6394</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5081</v>
+        <v>-0.0197</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6002</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6005</v>
+        <v>0.9737</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0449</v>
+        <v>1.3839</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2311</v>
+        <v>1.0097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.276</v>
+        <v>0.3742</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2806</v>
+        <v>-0.2795</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1606</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.12</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. SANTAMATILDE PERIS</t>
+          <t>A. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.51</v>
+        <v>0.0728</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2204</v>
+        <v>0.0397</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2896</v>
+        <v>0.0331</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.8749</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6821</v>
+        <v>-0.5132</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9911</v>
+        <v>-0.3618</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1019</v>
+        <v>0.6671</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.618</v>
+        <v>0.4644</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7199</v>
+        <v>0.2026</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7929</v>
+        <v>-1.542</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0641</v>
+        <v>-0.9776</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2712</v>
+        <v>-0.5644</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6002</v>
+        <v>1.5579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4192</v>
+        <v>0.5888</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3223</v>
+        <v>0.4495</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0969</v>
+        <v>0.1393</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.2253</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.1032</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. LUENGO MATEO</t>
+          <t>V. SANTAMATILDE PERIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.4714</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2745</v>
+        <v>-0.1826</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5734</v>
+        <v>-0.2888</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3233</v>
+        <v>-0.7063</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5518999999999999</v>
+        <v>-1.7016</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8752</v>
+        <v>0.9953</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5211</v>
+        <v>0.1265</v>
       </c>
       <c r="K10" t="n">
-        <v>1.2596</v>
+        <v>-0.6029</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.7807</v>
+        <v>0.7295</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8022</v>
+        <v>-0.8329</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7078</v>
+        <v>-1.0987</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0945</v>
+        <v>0.2658</v>
       </c>
       <c r="P10" t="n">
-        <v>2.0006</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0006</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2584</v>
+        <v>-0.3493</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7534</v>
+        <v>-0.3092</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5049</v>
+        <v>-0.0401</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5405</v>
+        <v>-1.4332</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9606</v>
+        <v>-1.9135</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4201</v>
+        <v>0.4803</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.1602</v>
+        <v>-2.1503</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3604</v>
+        <v>-1.3398</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.8105</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.974</v>
+        <v>-1.9319</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.296</v>
+        <v>-1.2674</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.678</v>
+        <v>-0.6645</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1862</v>
+        <v>-0.2184</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0643</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1219</v>
+        <v>-0.146</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0196</v>
+        <v>0.1329</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0134</v>
+        <v>0.0185</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0062</v>
+        <v>0.1144</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6141</v>
+        <v>-4.9078</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.881</v>
+        <v>-2.9381</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.733</v>
+        <v>-1.9698</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4163</v>
+        <v>-3.3788</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3425</v>
+        <v>0.3263</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7587</v>
+        <v>-3.7052</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4649</v>
+        <v>-1.2697</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9213</v>
+        <v>2.0039</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.3862</v>
+        <v>-3.2736</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9513</v>
+        <v>-2.1091</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5788</v>
+        <v>-1.6776</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0578</v>
+        <v>0.6073</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.6101</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0177</v>
+        <v>-0.0028</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5399</v>
+        <v>-1.5521</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3401</v>
+        <v>-0.3311</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.123900000000001</v>
+        <v>-7.7011</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.2593</v>
+        <v>-6.6334</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8645</v>
+        <v>-1.0677</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.7274</v>
+        <v>-3.693</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.7998</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.9276</v>
+        <v>-2.872</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1047</v>
+        <v>-1.9339</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0436</v>
+        <v>0.1078</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1483</v>
+        <v>-2.0418</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6227</v>
+        <v>-1.7591</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8434</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7793</v>
+        <v>-0.8302</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.0011</v>
+        <v>-3.8947</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0014</v>
+        <v>-4.8684</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1356</v>
+        <v>0.1661</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1533</v>
+        <v>0.1689</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0177</v>
+        <v>-0.0028</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.204699999999997</v>
+        <v>4.472900000000005</v>
       </c>
       <c r="E14" t="n">
-        <v>8.094800000000003</v>
+        <v>10.3784</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.889800000000001</v>
+        <v>-5.9056</v>
       </c>
       <c r="G14" t="n">
-        <v>-8.4236</v>
+        <v>-8.3422</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9996999999999993</v>
+        <v>1.0262</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.423400000000001</v>
+        <v>-9.3688</v>
       </c>
       <c r="J14" t="n">
-        <v>6.1601</v>
+        <v>7.498799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>9.824299999999999</v>
+        <v>10.5588</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.6643</v>
+        <v>-3.060099999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.5836</v>
+        <v>-15.841</v>
       </c>
       <c r="N14" t="n">
-        <v>-8.8245</v>
+        <v>-9.5326</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.7591</v>
+        <v>-6.3086</v>
       </c>
       <c r="P14" t="n">
-        <v>2.000699999999999</v>
+        <v>1.9474</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.0032</v>
+        <v>-10.7106</v>
       </c>
       <c r="R14" t="n">
-        <v>13.0038</v>
+        <v>12.6579</v>
       </c>
       <c r="S14" t="n">
-        <v>5.068299999999998</v>
+        <v>5.2699</v>
       </c>
       <c r="T14" t="n">
-        <v>4.1803</v>
+        <v>4.5871</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8881</v>
+        <v>0.6827999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>5.5595</v>
+        <v>5.5978</v>
       </c>
       <c r="W14" t="n">
-        <v>8.757400000000001</v>
+        <v>9.003100000000002</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.1979</v>
+        <v>-3.4054</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6479</v>
+        <v>2.6277</v>
       </c>
       <c r="E15" t="n">
-        <v>3.73</v>
+        <v>3.2787</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-0.6511</v>
       </c>
       <c r="G15" t="n">
-        <v>0.615</v>
+        <v>0.4944</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0172</v>
+        <v>-1.0695</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6322</v>
+        <v>1.5638</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6815</v>
+        <v>1.7455</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.8134</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9321</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0665</v>
+        <v>-1.2511</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7787</v>
+        <v>-1.8828</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7123</v>
+        <v>0.6317</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>1.593</v>
+        <v>0.6786</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0094</v>
+        <v>0.4153</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5837</v>
+        <v>0.2632</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1606</v>
+        <v>-0.1032</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0392</v>
+        <v>1.1179</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1131</v>
+        <v>2.4805</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2762</v>
+        <v>3.6441</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1631</v>
+        <v>-1.1636</v>
       </c>
       <c r="G16" t="n">
-        <v>5.7195</v>
+        <v>5.783</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3706</v>
+        <v>2.4211</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3489</v>
+        <v>3.3619</v>
       </c>
       <c r="J16" t="n">
-        <v>7.1422</v>
+        <v>7.3368</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4208</v>
+        <v>3.5434</v>
       </c>
       <c r="L16" t="n">
-        <v>3.7214</v>
+        <v>3.7934</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4227</v>
+        <v>-1.5538</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0502</v>
+        <v>-1.1223</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3725</v>
+        <v>-0.4315</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0454</v>
+        <v>0.1638</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0243</v>
+        <v>-0.0064</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.021</v>
+        <v>0.1703</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3604</v>
+        <v>-1.3242</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.8408</v>
+        <v>-0.7653</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5196</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2146</v>
+        <v>2.117</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4176</v>
+        <v>1.1311</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7971</v>
+        <v>0.9859</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1629</v>
+        <v>4.2899</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1858</v>
+        <v>1.2552</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9771</v>
+        <v>3.0347</v>
       </c>
       <c r="J17" t="n">
-        <v>4.094</v>
+        <v>4.3871</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3647</v>
+        <v>2.5223</v>
       </c>
       <c r="L17" t="n">
-        <v>1.7293</v>
+        <v>1.8648</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0689</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1789</v>
+        <v>-1.2671</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2478</v>
+        <v>1.1699</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2009</v>
+        <v>-3.1158</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1684</v>
+        <v>-0.3872</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4755</v>
+        <v>-0.1403</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6928</v>
+        <v>-0.2469</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1795</v>
+        <v>-0.2279</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3857</v>
+        <v>0.9991</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3653</v>
+        <v>0.7816</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0204</v>
+        <v>0.2174</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4375</v>
+        <v>0.4589</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9935</v>
+        <v>-0.9821</v>
       </c>
       <c r="I18" t="n">
-        <v>1.431</v>
+        <v>1.4411</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9454</v>
+        <v>1.0391</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3363</v>
+        <v>-0.2822</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2817</v>
+        <v>1.3213</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5079</v>
+        <v>-0.5802</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6573</v>
+        <v>-0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0521</v>
+        <v>-0.4335</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.2575</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.472</v>
+        <v>-0.1761</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,19 +1891,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.1329</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1918,10 +1918,10 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1356</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1356</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GOMEZ-ARRONES MORGADO</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8397</v>
+        <v>-0.0257</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7695</v>
+        <v>0.9341</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.6092</v>
+        <v>-0.9599</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6206</v>
+        <v>1.3752</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.4898</v>
+        <v>0.0313</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8692</v>
+        <v>1.3439</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3105</v>
+        <v>2.6631</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3181</v>
+        <v>2.0707</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0076</v>
+        <v>0.5924</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3101</v>
+        <v>-1.2879</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.1717</v>
+        <v>-2.0394</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8616</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8005</v>
+        <v>-1.1684</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2001</v>
+        <v>-3.1158</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0196</v>
+        <v>-0.8431</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08019999999999999</v>
+        <v>-0.4448</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0999</v>
+        <v>-0.3983</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1998</v>
+        <v>1.8316</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>A. GOMEZ-ARRONES MORGADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1289</v>
+        <v>-0.3414</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4297</v>
+        <v>0.9398</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6992</v>
+        <v>-1.2813</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3373</v>
+        <v>-1.751</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0244</v>
+        <v>-2.6002</v>
       </c>
       <c r="I21" t="n">
-        <v>1.313</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3762</v>
+        <v>-0.1973</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9249</v>
+        <v>-0.295</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4514</v>
+        <v>0.0978</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0389</v>
+        <v>-1.5537</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9005</v>
+        <v>-2.3052</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8616</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2003</v>
+        <v>1.7526</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.2009</v>
+        <v>-0.1947</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8657</v>
+        <v>-0.3431</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4047</v>
+        <v>0.1108</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4611</v>
+        <v>-0.4539</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5999</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7997</v>
+        <v>1.2211</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6982</v>
+        <v>-3.5029</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7321</v>
+        <v>-0.5279</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9661</v>
+        <v>-2.975</v>
       </c>
       <c r="G22" t="n">
-        <v>0.483</v>
+        <v>0.433</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4312</v>
+        <v>0.43</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0518</v>
+        <v>0.003</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8416</v>
+        <v>0.8934</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6816</v>
+        <v>0.7313</v>
       </c>
       <c r="L22" t="n">
-        <v>0.16</v>
+        <v>0.1621</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3586</v>
+        <v>-0.4604</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2505</v>
+        <v>-0.3013</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1082</v>
+        <v>-0.1591</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5816</v>
+        <v>-0.299</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>-0.2529</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2082</v>
+        <v>-0.0462</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.9994</v>
+        <v>-3.0526</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8992</v>
+        <v>-5.3281</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5069</v>
+        <v>-4.2759</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3924</v>
+        <v>-1.0522</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8464</v>
+        <v>-2.874</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.645</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.1997</v>
+        <v>-2.229</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1867</v>
+        <v>-2.0268</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3253</v>
+        <v>0.4286</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.512</v>
+        <v>-2.4554</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6597</v>
+        <v>-0.8472</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9721</v>
+        <v>-1.0736</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3123</v>
+        <v>0.2264</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S23" t="n">
-        <v>0.207</v>
+        <v>-0.1747</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8804999999999999</v>
+        <v>-0.107</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6735</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4596</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2047</v>
+        <v>-0.8409000000000004</v>
       </c>
       <c r="E24" t="n">
-        <v>3.8899</v>
+        <v>5.9056</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.0946</v>
+        <v>-6.7469</v>
       </c>
       <c r="G24" t="n">
-        <v>8.4238</v>
+        <v>8.3423</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9995999999999998</v>
+        <v>-1.0263</v>
       </c>
       <c r="I24" t="n">
-        <v>9.423499999999999</v>
+        <v>9.3687</v>
       </c>
       <c r="J24" t="n">
-        <v>14.5837</v>
+        <v>15.8409</v>
       </c>
       <c r="K24" t="n">
-        <v>8.824499999999999</v>
+        <v>9.532499999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>5.7593</v>
+        <v>6.3085</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.1599</v>
+        <v>-7.498600000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>-9.824299999999999</v>
+        <v>-10.5588</v>
       </c>
       <c r="O24" t="n">
-        <v>3.664200000000001</v>
+        <v>3.0602</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0005</v>
+        <v>-1.9473</v>
       </c>
       <c r="Q24" t="n">
-        <v>-13.0037</v>
+        <v>-12.6578</v>
       </c>
       <c r="R24" t="n">
-        <v>11.0033</v>
+        <v>10.7106</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.0684</v>
+        <v>-1.6382</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8878999999999998</v>
+        <v>-0.6828000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.1804</v>
+        <v>-0.9555</v>
       </c>
       <c r="V24" t="n">
-        <v>-5.559600000000001</v>
+        <v>-5.5979</v>
       </c>
       <c r="W24" t="n">
-        <v>3.1979</v>
+        <v>3.4053</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.7575</v>
+        <v>-9.003299999999999</v>
       </c>
     </row>
   </sheetData>
